--- a/data/externalStats/File1/RPT_RPT9537148419924KB_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT9537148419924KB_externalStats.xlsx
@@ -2104,7 +2104,7 @@
         <v>4892836.646637341</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>7094.093971315898</v>
+        <v>7094.093971315897</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="AN25" s="48" t="n">
-        <v>5844.968260512382</v>
+        <v>5844.968260512383</v>
       </c>
     </row>
     <row r="26">
@@ -2140,7 +2140,7 @@
         <v>1512698</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.40619635890768</v>
+        <v>96.40619635890766</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>75.65759727918376</v>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>1512043.286485777</v>
+        <v>1512043.286485776</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>3060.609005713499</v>
@@ -2371,7 +2371,7 @@
         <v>278616</v>
       </c>
       <c r="G29" s="62" t="n">
-        <v>74.07897211681242</v>
+        <v>74.07897211681244</v>
       </c>
       <c r="H29" s="63" t="n">
         <v>45.96865203761755</v>
@@ -2442,13 +2442,13 @@
         <v>74771</v>
       </c>
       <c r="E30" s="71" t="n">
-        <v>3850509.280000001</v>
+        <v>3850509.28</v>
       </c>
       <c r="F30" s="71" t="n">
         <v>3001023</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>51.49736234636424</v>
+        <v>51.49736234636423</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>40.13618916424817</v>
@@ -2659,7 +2659,7 @@
         <v>5208274</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>54.88143800936842</v>
+        <v>54.88143800936843</v>
       </c>
       <c r="H33" s="42" t="n">
         <v>24.13126010628686</v>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>556393.580935954</v>
+        <v>556393.5809359541</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>827.1029214485164</v>
+        <v>827.1029214485163</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -2884,13 +2884,13 @@
         <v>444347</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>35681711.26499999</v>
+        <v>35681711.265</v>
       </c>
       <c r="F36" s="66" t="n">
         <v>25091574</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>80.30145644057458</v>
+        <v>80.3014564405746</v>
       </c>
       <c r="H36" s="68" t="n">
         <v>56.46842220156769</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="AN36" s="58" t="n">
-        <v>4.737683294822233</v>
+        <v>4.737683294822232</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickBot="1">
@@ -3038,13 +3038,13 @@
         <v>445256</v>
       </c>
       <c r="E38" s="71" t="n">
-        <v>35791437.665</v>
+        <v>35791437.66500001</v>
       </c>
       <c r="F38" s="71" t="n">
         <v>25131826</v>
       </c>
       <c r="G38" s="72" t="n">
-        <v>80.38395364689077</v>
+        <v>80.38395364689079</v>
       </c>
       <c r="H38" s="73" t="n">
         <v>56.44354259122841</v>
@@ -3215,7 +3215,7 @@
         <v>402905.5641328274</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>49.94371127615922</v>
+        <v>49.94371127615923</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -3251,7 +3251,7 @@
         <v>6388064</v>
       </c>
       <c r="G41" s="41" t="n">
-        <v>50.26792547888586</v>
+        <v>50.26792547888587</v>
       </c>
       <c r="H41" s="42" t="n">
         <v>24.17825417191823</v>
@@ -3482,7 +3482,7 @@
         <v>27813981</v>
       </c>
       <c r="G44" s="67" t="n">
-        <v>76.17716529547398</v>
+        <v>76.177165295474</v>
       </c>
       <c r="H44" s="68" t="n">
         <v>54.21226296493372</v>
@@ -3553,13 +3553,13 @@
         <v>6970</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>558719.05</v>
+        <v>558719.0500000002</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>318868</v>
       </c>
       <c r="G45" s="62" t="n">
-        <v>80.16055236728839</v>
+        <v>80.1605523672884</v>
       </c>
       <c r="H45" s="63" t="n">
         <v>45.74863701578192</v>
@@ -3595,13 +3595,13 @@
         <v>520027</v>
       </c>
       <c r="E46" s="71" t="n">
-        <v>39641946.945</v>
+        <v>39641946.94500001</v>
       </c>
       <c r="F46" s="71" t="n">
         <v>28132849</v>
       </c>
       <c r="G46" s="72" t="n">
-        <v>76.23055523078609</v>
+        <v>76.23055523078611</v>
       </c>
       <c r="H46" s="73" t="n">
         <v>54.09882371492249</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>174475.6257716984</v>
+        <v>174475.6257716985</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>123.5809516464353</v>
@@ -4715,49 +4715,49 @@
         <v>0</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -5126,49 +5126,49 @@
         <v>0</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -7211,49 +7211,49 @@
         <v>0</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
     </row>
     <row r="100">
@@ -7550,49 +7550,49 @@
         <v>0</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>6251003.904760483</v>
+        <v>6251003.904760482</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>8867.617464144872</v>
@@ -8664,7 +8664,7 @@
         <v>1512698</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.40619635890768</v>
+        <v>96.40619635890766</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>75.65759727918376</v>
@@ -8702,10 +8702,10 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>3169446.483118858</v>
+        <v>3169446.483118857</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>4679.66281802372</v>
+        <v>4679.662818023719</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -8895,7 +8895,7 @@
         <v>278616</v>
       </c>
       <c r="G29" s="62" t="n">
-        <v>74.07897211681242</v>
+        <v>74.07897211681244</v>
       </c>
       <c r="H29" s="63" t="n">
         <v>45.96865203761755</v>
@@ -8966,13 +8966,13 @@
         <v>74771</v>
       </c>
       <c r="E30" s="71" t="n">
-        <v>3850509.280000001</v>
+        <v>3850509.28</v>
       </c>
       <c r="F30" s="71" t="n">
         <v>3001023</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>51.49736234636424</v>
+        <v>51.49736234636423</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>40.13618916424817</v>
@@ -9183,7 +9183,7 @@
         <v>5208274</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>54.88143800936842</v>
+        <v>54.88143800936843</v>
       </c>
       <c r="H33" s="42" t="n">
         <v>24.13126010628686</v>
@@ -9408,13 +9408,13 @@
         <v>444347</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>35681711.26499999</v>
+        <v>35681711.265</v>
       </c>
       <c r="F36" s="66" t="n">
         <v>25091574</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>80.30145644057458</v>
+        <v>80.3014564405746</v>
       </c>
       <c r="H36" s="68" t="n">
         <v>56.46842220156769</v>
@@ -9562,13 +9562,13 @@
         <v>445256</v>
       </c>
       <c r="E38" s="71" t="n">
-        <v>35791437.665</v>
+        <v>35791437.66500001</v>
       </c>
       <c r="F38" s="71" t="n">
         <v>25131826</v>
       </c>
       <c r="G38" s="72" t="n">
-        <v>80.38395364689077</v>
+        <v>80.38395364689079</v>
       </c>
       <c r="H38" s="73" t="n">
         <v>56.44354259122841</v>
@@ -9672,7 +9672,7 @@
         <v>432982.3623017127</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>747.2463417280802</v>
+        <v>747.2463417280803</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -9775,7 +9775,7 @@
         <v>6388064</v>
       </c>
       <c r="G41" s="41" t="n">
-        <v>50.26792547888586</v>
+        <v>50.26792547888587</v>
       </c>
       <c r="H41" s="42" t="n">
         <v>24.17825417191823</v>
@@ -9890,10 +9890,10 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>354323.1051082383</v>
+        <v>354323.1051082382</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>5884.096164825529</v>
+        <v>5884.096164825528</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -10006,7 +10006,7 @@
         <v>27813981</v>
       </c>
       <c r="G44" s="67" t="n">
-        <v>76.17716529547398</v>
+        <v>76.177165295474</v>
       </c>
       <c r="H44" s="68" t="n">
         <v>54.21226296493372</v>
@@ -10077,13 +10077,13 @@
         <v>6970</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>558719.05</v>
+        <v>558719.0500000002</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>318868</v>
       </c>
       <c r="G45" s="62" t="n">
-        <v>80.16055236728839</v>
+        <v>80.1605523672884</v>
       </c>
       <c r="H45" s="63" t="n">
         <v>45.74863701578192</v>
@@ -10119,13 +10119,13 @@
         <v>520027</v>
       </c>
       <c r="E46" s="71" t="n">
-        <v>39641946.945</v>
+        <v>39641946.94500001</v>
       </c>
       <c r="F46" s="71" t="n">
         <v>28132849</v>
       </c>
       <c r="G46" s="72" t="n">
-        <v>76.23055523078609</v>
+        <v>76.23055523078611</v>
       </c>
       <c r="H46" s="73" t="n">
         <v>54.09882371492249</v>
@@ -10404,7 +10404,7 @@
         <v>1441332.43069695</v>
       </c>
       <c r="AH52" s="56" t="n">
-        <v>5112.416745915412</v>
+        <v>5112.416745915413</v>
       </c>
     </row>
     <row r="53">
@@ -10563,7 +10563,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>964063.903042457</v>
+        <v>964063.9030424568</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>869.1107671791891</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>775001.525733977</v>
+        <v>775001.5257339771</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>698.6927886959031</v>
@@ -11052,7 +11052,7 @@
         <v>246103.3308430436</v>
       </c>
       <c r="AH60" s="56" t="n">
-        <v>471.8857716342978</v>
+        <v>471.8857716342977</v>
       </c>
     </row>
     <row r="61">
@@ -11239,49 +11239,49 @@
         <v>0</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11462,7 +11462,7 @@
         <v>152593.7608721495</v>
       </c>
       <c r="AH65" s="56" t="n">
-        <v>416.9416153741438</v>
+        <v>416.9416153741437</v>
       </c>
     </row>
     <row r="66">
@@ -11650,49 +11650,49 @@
         <v>0</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -13735,49 +13735,49 @@
         <v>0</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
     </row>
     <row r="100">
@@ -14074,49 +14074,49 @@
         <v>0</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>7751682.483459943</v>
+        <v>7751682.483459942</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>10641.14095697385</v>
@@ -15188,7 +15188,7 @@
         <v>1512698</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.40619635890768</v>
+        <v>96.40619635890766</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>75.65759727918376</v>
@@ -15383,7 +15383,7 @@
         <v>1695643.9826171</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>5346.493559269546</v>
+        <v>5346.493559269547</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -15419,7 +15419,7 @@
         <v>278616</v>
       </c>
       <c r="G29" s="62" t="n">
-        <v>74.07897211681242</v>
+        <v>74.07897211681244</v>
       </c>
       <c r="H29" s="63" t="n">
         <v>45.96865203761755</v>
@@ -15490,13 +15490,13 @@
         <v>74771</v>
       </c>
       <c r="E30" s="71" t="n">
-        <v>3850509.280000001</v>
+        <v>3850509.28</v>
       </c>
       <c r="F30" s="71" t="n">
         <v>3001023</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>51.49736234636424</v>
+        <v>51.49736234636423</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>40.13618916424817</v>
@@ -15707,7 +15707,7 @@
         <v>5208274</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>54.88143800936842</v>
+        <v>54.88143800936843</v>
       </c>
       <c r="H33" s="42" t="n">
         <v>24.13126010628686</v>
@@ -15822,10 +15822,10 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>723531.9493912427</v>
+        <v>723531.9493912426</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>896.2858789679237</v>
+        <v>896.2858789679236</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -15899,10 +15899,10 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>694955.4965220469</v>
+        <v>694955.496522047</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>72.12326121359592</v>
+        <v>72.12326121359591</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -15932,13 +15932,13 @@
         <v>444347</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>35681711.26499999</v>
+        <v>35681711.265</v>
       </c>
       <c r="F36" s="66" t="n">
         <v>25091574</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>80.30145644057458</v>
+        <v>80.3014564405746</v>
       </c>
       <c r="H36" s="68" t="n">
         <v>56.46842220156769</v>
@@ -16072,7 +16072,7 @@
         </is>
       </c>
       <c r="AN37" s="58" t="n">
-        <v>61.7871117037524</v>
+        <v>61.78711170375239</v>
       </c>
     </row>
     <row r="38" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -16086,13 +16086,13 @@
         <v>445256</v>
       </c>
       <c r="E38" s="71" t="n">
-        <v>35791437.665</v>
+        <v>35791437.66500001</v>
       </c>
       <c r="F38" s="71" t="n">
         <v>25131826</v>
       </c>
       <c r="G38" s="72" t="n">
-        <v>80.38395364689077</v>
+        <v>80.38395364689079</v>
       </c>
       <c r="H38" s="73" t="n">
         <v>56.44354259122841</v>
@@ -16299,7 +16299,7 @@
         <v>6388064</v>
       </c>
       <c r="G41" s="41" t="n">
-        <v>50.26792547888586</v>
+        <v>50.26792547888587</v>
       </c>
       <c r="H41" s="42" t="n">
         <v>24.17825417191823</v>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>232740.7056095824</v>
+        <v>232740.7056095825</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>212.4125022456222</v>
@@ -16530,7 +16530,7 @@
         <v>27813981</v>
       </c>
       <c r="G44" s="67" t="n">
-        <v>76.17716529547398</v>
+        <v>76.177165295474</v>
       </c>
       <c r="H44" s="68" t="n">
         <v>54.21226296493372</v>
@@ -16601,13 +16601,13 @@
         <v>6970</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>558719.05</v>
+        <v>558719.0500000002</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>318868</v>
       </c>
       <c r="G45" s="62" t="n">
-        <v>80.16055236728839</v>
+        <v>80.1605523672884</v>
       </c>
       <c r="H45" s="63" t="n">
         <v>45.74863701578192</v>
@@ -16643,13 +16643,13 @@
         <v>520027</v>
       </c>
       <c r="E46" s="71" t="n">
-        <v>39641946.945</v>
+        <v>39641946.94500001</v>
       </c>
       <c r="F46" s="71" t="n">
         <v>28132849</v>
       </c>
       <c r="G46" s="72" t="n">
-        <v>76.23055523078609</v>
+        <v>76.23055523078611</v>
       </c>
       <c r="H46" s="73" t="n">
         <v>54.09882371492249</v>
@@ -17763,49 +17763,49 @@
         <v>0</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -18174,49 +18174,49 @@
         <v>0</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -20259,49 +20259,49 @@
         <v>0</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
     </row>
     <row r="100">
@@ -20598,49 +20598,49 @@
         <v>0</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -21712,7 +21712,7 @@
         <v>1512698</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.40619635890768</v>
+        <v>96.40619635890766</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>75.65759727918376</v>
@@ -21753,7 +21753,7 @@
         <v>4260413.832362346</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>5765.812558087028</v>
+        <v>5765.812558087027</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -21943,7 +21943,7 @@
         <v>278616</v>
       </c>
       <c r="G29" s="62" t="n">
-        <v>74.07897211681242</v>
+        <v>74.07897211681244</v>
       </c>
       <c r="H29" s="63" t="n">
         <v>45.96865203761755</v>
@@ -22014,13 +22014,13 @@
         <v>74771</v>
       </c>
       <c r="E30" s="71" t="n">
-        <v>3850509.280000001</v>
+        <v>3850509.28</v>
       </c>
       <c r="F30" s="71" t="n">
         <v>3001023</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>51.49736234636424</v>
+        <v>51.49736234636423</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>40.13618916424817</v>
@@ -22231,7 +22231,7 @@
         <v>5208274</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>54.88143800936842</v>
+        <v>54.88143800936843</v>
       </c>
       <c r="H33" s="42" t="n">
         <v>24.13126010628686</v>
@@ -22456,13 +22456,13 @@
         <v>444347</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>35681711.26499999</v>
+        <v>35681711.265</v>
       </c>
       <c r="F36" s="66" t="n">
         <v>25091574</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>80.30145644057458</v>
+        <v>80.3014564405746</v>
       </c>
       <c r="H36" s="68" t="n">
         <v>56.46842220156769</v>
@@ -22596,7 +22596,7 @@
         </is>
       </c>
       <c r="AN37" s="58" t="n">
-        <v>2086.013747913035</v>
+        <v>2086.013747913036</v>
       </c>
     </row>
     <row r="38" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -22610,13 +22610,13 @@
         <v>445256</v>
       </c>
       <c r="E38" s="71" t="n">
-        <v>35791437.665</v>
+        <v>35791437.66500001</v>
       </c>
       <c r="F38" s="71" t="n">
         <v>25131826</v>
       </c>
       <c r="G38" s="72" t="n">
-        <v>80.38395364689077</v>
+        <v>80.38395364689079</v>
       </c>
       <c r="H38" s="73" t="n">
         <v>56.44354259122841</v>
@@ -22784,7 +22784,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>467965.6858161185</v>
+        <v>467965.6858161184</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>745.1977318077995</v>
@@ -22823,7 +22823,7 @@
         <v>6388064</v>
       </c>
       <c r="G41" s="41" t="n">
-        <v>50.26792547888586</v>
+        <v>50.26792547888587</v>
       </c>
       <c r="H41" s="42" t="n">
         <v>24.17825417191823</v>
@@ -23054,7 +23054,7 @@
         <v>27813981</v>
       </c>
       <c r="G44" s="67" t="n">
-        <v>76.17716529547398</v>
+        <v>76.177165295474</v>
       </c>
       <c r="H44" s="68" t="n">
         <v>54.21226296493372</v>
@@ -23125,13 +23125,13 @@
         <v>6970</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>558719.05</v>
+        <v>558719.0500000002</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>318868</v>
       </c>
       <c r="G45" s="62" t="n">
-        <v>80.16055236728839</v>
+        <v>80.1605523672884</v>
       </c>
       <c r="H45" s="63" t="n">
         <v>45.74863701578192</v>
@@ -23167,13 +23167,13 @@
         <v>520027</v>
       </c>
       <c r="E46" s="71" t="n">
-        <v>39641946.945</v>
+        <v>39641946.94500001</v>
       </c>
       <c r="F46" s="71" t="n">
         <v>28132849</v>
       </c>
       <c r="G46" s="72" t="n">
-        <v>76.23055523078609</v>
+        <v>76.23055523078611</v>
       </c>
       <c r="H46" s="73" t="n">
         <v>54.09882371492249</v>
@@ -23773,7 +23773,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>467965.6858161185</v>
+        <v>467965.6858161184</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>767.6697553968106</v>
@@ -24181,7 +24181,7 @@
         <v>178688.4697746161</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>416.2938181268347</v>
+        <v>416.2938181268346</v>
       </c>
     </row>
     <row r="62">
@@ -24287,49 +24287,49 @@
         <v>0</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24421,7 +24421,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>151874.4287357912</v>
+        <v>151874.4287357911</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>508.2383233292842</v>
@@ -24698,49 +24698,49 @@
         <v>0</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -26783,49 +26783,49 @@
         <v>0</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
     </row>
     <row r="100">
@@ -27122,49 +27122,49 @@
         <v>0</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -28236,7 +28236,7 @@
         <v>1512698</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>96.40619635890768</v>
+        <v>96.40619635890766</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>75.65759727918376</v>
@@ -28277,7 +28277,7 @@
         <v>4970140.600484848</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>6400.051939476602</v>
+        <v>6400.051939476601</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>1602883.34179394</v>
+        <v>1602883.341793941</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>1161.939686773654</v>
@@ -28467,7 +28467,7 @@
         <v>278616</v>
       </c>
       <c r="G29" s="62" t="n">
-        <v>74.07897211681242</v>
+        <v>74.07897211681244</v>
       </c>
       <c r="H29" s="63" t="n">
         <v>45.96865203761755</v>
@@ -28538,13 +28538,13 @@
         <v>74771</v>
       </c>
       <c r="E30" s="71" t="n">
-        <v>3850509.280000001</v>
+        <v>3850509.28</v>
       </c>
       <c r="F30" s="71" t="n">
         <v>3001023</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>51.49736234636424</v>
+        <v>51.49736234636423</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>40.13618916424817</v>
@@ -28755,7 +28755,7 @@
         <v>5208274</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>54.88143800936842</v>
+        <v>54.88143800936843</v>
       </c>
       <c r="H33" s="42" t="n">
         <v>24.13126010628686</v>
@@ -28980,13 +28980,13 @@
         <v>444347</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>35681711.26499999</v>
+        <v>35681711.265</v>
       </c>
       <c r="F36" s="66" t="n">
         <v>25091574</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>80.30145644057458</v>
+        <v>80.3014564405746</v>
       </c>
       <c r="H36" s="68" t="n">
         <v>56.46842220156769</v>
@@ -29134,13 +29134,13 @@
         <v>445256</v>
       </c>
       <c r="E38" s="71" t="n">
-        <v>35791437.665</v>
+        <v>35791437.66500001</v>
       </c>
       <c r="F38" s="71" t="n">
         <v>25131826</v>
       </c>
       <c r="G38" s="72" t="n">
-        <v>80.38395364689077</v>
+        <v>80.38395364689079</v>
       </c>
       <c r="H38" s="73" t="n">
         <v>56.44354259122841</v>
@@ -29347,7 +29347,7 @@
         <v>6388064</v>
       </c>
       <c r="G41" s="41" t="n">
-        <v>50.26792547888586</v>
+        <v>50.26792547888587</v>
       </c>
       <c r="H41" s="42" t="n">
         <v>24.17825417191823</v>
@@ -29385,7 +29385,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>272901.3316407848</v>
+        <v>272901.3316407847</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>224.4086305367263</v>
@@ -29578,7 +29578,7 @@
         <v>27813981</v>
       </c>
       <c r="G44" s="67" t="n">
-        <v>76.17716529547398</v>
+        <v>76.177165295474</v>
       </c>
       <c r="H44" s="68" t="n">
         <v>54.21226296493372</v>
@@ -29649,13 +29649,13 @@
         <v>6970</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>558719.05</v>
+        <v>558719.0500000002</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>318868</v>
       </c>
       <c r="G45" s="62" t="n">
-        <v>80.16055236728839</v>
+        <v>80.1605523672884</v>
       </c>
       <c r="H45" s="63" t="n">
         <v>45.74863701578192</v>
@@ -29691,13 +29691,13 @@
         <v>520027</v>
       </c>
       <c r="E46" s="71" t="n">
-        <v>39641946.945</v>
+        <v>39641946.94500001</v>
       </c>
       <c r="F46" s="71" t="n">
         <v>28132849</v>
       </c>
       <c r="G46" s="72" t="n">
-        <v>76.23055523078609</v>
+        <v>76.23055523078611</v>
       </c>
       <c r="H46" s="73" t="n">
         <v>54.09882371492249</v>
@@ -29976,7 +29976,7 @@
         <v>2079924.973872326</v>
       </c>
       <c r="AH52" s="56" t="n">
-        <v>4248.655610534054</v>
+        <v>4248.655610534055</v>
       </c>
     </row>
     <row r="53">
@@ -30138,7 +30138,7 @@
         <v>1360701.851253651</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>961.5258064317815</v>
+        <v>961.5258064317813</v>
       </c>
     </row>
     <row r="55">
@@ -30624,7 +30624,7 @@
         <v>255651.8598179875</v>
       </c>
       <c r="AH60" s="56" t="n">
-        <v>604.4211626238737</v>
+        <v>604.4211626238736</v>
       </c>
     </row>
     <row r="61">
@@ -30705,7 +30705,7 @@
         <v>241053.7570896112</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>582.9831014558807</v>
+        <v>582.9831014558808</v>
       </c>
     </row>
     <row r="62">
@@ -30811,49 +30811,49 @@
         <v>0</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -31197,7 +31197,7 @@
         <v>96125.75571735601</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>54.47251059500984</v>
+        <v>54.47251059500983</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -31222,49 +31222,49 @@
         <v>0</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -33307,49 +33307,49 @@
         <v>0</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
     </row>
     <row r="100">
@@ -33646,49 +33646,49 @@
         <v>0</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>153.9376778700135</v>
+        <v>153.9376778700148</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>72.28203457856003</v>
+        <v>72.28203457856034</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>1.293503069924507</v>
+        <v>1.293503069924518</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410075</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595071</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782967</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>26.22748476337624</v>
+        <v>26.22748476337645</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>0.4164758392767124</v>
+        <v>0.4164758392767203</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>413.5483367949296</v>
+        <v>413.5483367949291</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>535.0409055454111</v>
+        <v>535.040905545412</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>96.17911912393895</v>
+        <v>96.17911912394001</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>21.08529797588732</v>
+        <v>21.08529797588746</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>0.4472220454100387</v>
+        <v>0.4472220454100455</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.3225561741564</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193939</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
